--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260616.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260616.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>13.74%</t>
+          <t>13.61%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.38%</t>
+          <t>10.53%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.25%</t>
+          <t>6.21%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.57%</t>
+          <t>6.09%</t>
         </is>
       </c>
     </row>
@@ -704,51 +704,51 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.17%</t>
+          <t>5.45%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>環球晶圓</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>4,828,000</t>
+          <t>6,042,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.76%</t>
+          <t>4.49%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>環球晶圓</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>6,042,000</t>
+          <t>4,828,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.10%</t>
+          <t>4.27%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
@@ -814,73 +814,73 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.60%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>文曄科技</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>2,827,000</t>
+          <t>15,276,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.38%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>文曄科技</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>15,276,000</t>
+          <t>19,558,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.38%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>19,558,000</t>
+          <t>2,827,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.24%</t>
         </is>
       </c>
     </row>
@@ -931,66 +931,66 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>台灣積體</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>12,063,000</t>
+          <t>1,101,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>台灣積體</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>1,101,000</t>
+          <t>14,856,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>14,856,000</t>
+          <t>12,063,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
@@ -1056,73 +1056,73 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>7,181,000</t>
+          <t>4,558,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>和碩聯合</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>23,608,000</t>
+          <t>7,181,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>和碩聯合</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>4,558,000</t>
+          <t>23,608,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -1210,46 +1210,46 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>家登精密</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2,697,000</t>
+          <t>14,453,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>家登精密</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1,868,000</t>
+          <t>2,697,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>14,453,000</t>
+          <t>1,868,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>940,774,378</t>
+          <t>941,382,378</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1386,24 +1386,24 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>3,412,000</t>
+          <t>1,755,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,22 +1415,22 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1,755,000</t>
+          <t>3,412,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.14%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.01%</t>
         </is>
       </c>
     </row>
